--- a/Test Design/DemoQA-Test Design.xlsx
+++ b/Test Design/DemoQA-Test Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/939c1bf4b082bbe3/Desktop/Projects/Testing Projects/References/Hands-on Exercise/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenova\OneDrive\Desktop\TestingDocumentation\Test Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC1048CAE1D9486A5ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E39FBDD-0D8C-49A2-97DB-AE769C9403A8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC40D7B-0C48-417E-AB62-621760918761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement Elicitation" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="331">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -1358,9 +1358,6 @@
     <t>Test Execution Level</t>
   </si>
   <si>
-    <t>TC001-01</t>
-  </si>
-  <si>
     <t>Validate text input submission</t>
   </si>
   <si>
@@ -1370,9 +1367,6 @@
     <t>Entered text should be displayed correctly in the output section.</t>
   </si>
   <si>
-    <t>TC001-02</t>
-  </si>
-  <si>
     <t>Verify error message for invalid email</t>
   </si>
   <si>
@@ -1385,9 +1379,6 @@
     <t>System should show an error message for invalid email format.</t>
   </si>
   <si>
-    <t>TC002-01</t>
-  </si>
-  <si>
     <t>Validate checkbox selection and deselection</t>
   </si>
   <si>
@@ -1397,9 +1388,6 @@
     <t>Checkboxes should behave correctly, selecting/deselecting as per user interaction.</t>
   </si>
   <si>
-    <t>TC002-02</t>
-  </si>
-  <si>
     <t>Verify behavior of partially selected checkboxes</t>
   </si>
   <si>
@@ -1409,9 +1397,6 @@
     <t>Parent checkbox should show a partial selection state when only some child checkboxes are selected.</t>
   </si>
   <si>
-    <t>TC003-01</t>
-  </si>
-  <si>
     <t>Validate radio button selection behavior</t>
   </si>
   <si>
@@ -1421,9 +1406,6 @@
     <t>Only one radio button should be selectable at a time.</t>
   </si>
   <si>
-    <t>TC004-01</t>
-  </si>
-  <si>
     <t>Validate adding a new record</t>
   </si>
   <si>
@@ -1433,9 +1415,6 @@
     <t>Record should be successfully added and displayed in the table.</t>
   </si>
   <si>
-    <t>TC004-02</t>
-  </si>
-  <si>
     <t>Validate search functionality</t>
   </si>
   <si>
@@ -1445,9 +1424,6 @@
     <t>Search should filter and display only relevant records.</t>
   </si>
   <si>
-    <t>TC004-03</t>
-  </si>
-  <si>
     <t>Verify edit functionality</t>
   </si>
   <si>
@@ -1457,9 +1433,6 @@
     <t>Edited details should be successfully saved and updated in the table.</t>
   </si>
   <si>
-    <t>TC004-04</t>
-  </si>
-  <si>
     <t>Verify record deletion</t>
   </si>
   <si>
@@ -1469,9 +1442,6 @@
     <t>Record should be removed from the table after deletion.</t>
   </si>
   <si>
-    <t>TC005-01</t>
-  </si>
-  <si>
     <t>Validate normal button click</t>
   </si>
   <si>
@@ -1481,9 +1451,6 @@
     <t>Success message should appear.</t>
   </si>
   <si>
-    <t>TC005-02</t>
-  </si>
-  <si>
     <t>Validate double-click functionality</t>
   </si>
   <si>
@@ -1493,9 +1460,6 @@
     <t>Success message should appear for double-click.</t>
   </si>
   <si>
-    <t>TC005-03</t>
-  </si>
-  <si>
     <t>Validate right-click functionality</t>
   </si>
   <si>
@@ -1505,9 +1469,6 @@
     <t>Success message should appear for right-click.</t>
   </si>
   <si>
-    <t>TC006-01</t>
-  </si>
-  <si>
     <t>Validate working links</t>
   </si>
   <si>
@@ -1517,9 +1478,6 @@
     <t>User should be navigated to the home page.</t>
   </si>
   <si>
-    <t>TC006-02</t>
-  </si>
-  <si>
     <t>Validate broken link behavior</t>
   </si>
   <si>
@@ -1529,9 +1487,6 @@
     <t>System should display a 404 error page.</t>
   </si>
   <si>
-    <t>TC007-01</t>
-  </si>
-  <si>
     <t>Validate file upload</t>
   </si>
   <si>
@@ -1541,9 +1496,6 @@
     <t>File should be successfully uploaded, and a success message should be displayed.</t>
   </si>
   <si>
-    <t>TC007-02</t>
-  </si>
-  <si>
     <t>Validate file download</t>
   </si>
   <si>
@@ -1551,9 +1503,6 @@
   </si>
   <si>
     <t>File should be downloaded successfully.</t>
-  </si>
-  <si>
-    <t>TC008-01</t>
   </si>
   <si>
     <t>Validate dynamic button appearance</t>
@@ -1613,9 +1562,6 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>TC001-03</t>
-  </si>
-  <si>
     <t>Validate text input submission at edge level</t>
   </si>
   <si>
@@ -1623,6 +1569,39 @@
   </si>
   <si>
     <t>Details of the form input are not be displayed</t>
+  </si>
+  <si>
+    <t>Regression,E2E</t>
+  </si>
+  <si>
+    <t>Regression, E2E</t>
+  </si>
+  <si>
+    <t>TestMethod</t>
+  </si>
+  <si>
+    <t>Validate forms inputs and submissions</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>TS001</t>
+  </si>
+  <si>
+    <t>TS002</t>
+  </si>
+  <si>
+    <t>TS003</t>
+  </si>
+  <si>
+    <t>TS004</t>
   </si>
 </sst>
 </file>
@@ -4005,7 +3984,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A0535F-E9BA-4BD0-B898-820EEEB24304}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr defaultColWidth="23.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="10" bestFit="1" customWidth="1"/>
@@ -4013,24 +3992,23 @@
     <col min="3" max="3" width="19.140625" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.7109375" style="10" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.140625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="27.140625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="49" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.140625" style="10" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="23.5703125" style="10"/>
+    <col min="6" max="8" width="28.140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.140625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="27.140625" style="10" customWidth="1"/>
+    <col min="15" max="15" width="49" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.140625" style="10" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="23.5703125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -4047,49 +4025,52 @@
         <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>239</v>
+        <v>322</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>109</v>
       </c>
@@ -4103,48 +4084,53 @@
         <v>138</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="7" t="str">
+        <f>SUBSTITUTE(PROPER(H2)," ","")</f>
+        <v>Mod-01-Ts-001_Tc001_ValidateTextInputSubmission</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A2,E2,F2)</f>
+        <v>MOD-01-TS-001_TC001_Validate text input submission</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="7">
+        <v>2</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="7">
-        <v>2</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>327</v>
-      </c>
       <c r="O2" s="7" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="R2" s="7"/>
+        <v>312</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="S2" s="7"/>
-    </row>
-    <row r="3" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="T2" s="7"/>
+    </row>
+    <row r="3" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>109</v>
       </c>
@@ -4158,48 +4144,53 @@
         <v>138</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <f t="shared" ref="G3:G40" si="0">SUBSTITUTE(PROPER(H3)," ","")</f>
+        <v>Mod-01-Ts-001_Tc002_VerifyErrorMessageForInvalidEmail</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A3,E3,F3)</f>
+        <v>MOD-01-TS-001_TC002_Verify error message for invalid email</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="J3" s="7">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="7">
-        <v>2</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="N3" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>329</v>
-      </c>
       <c r="Q3" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="R3" s="7"/>
+        <v>312</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="S3" s="7"/>
-    </row>
-    <row r="4" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="T3" s="7"/>
+    </row>
+    <row r="4" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>109</v>
       </c>
@@ -4213,48 +4204,53 @@
         <v>138</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H4" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-001_Tc003_ValidateTextInputSubmissionAtEdgeLevel</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A4,E4,F4)</f>
+        <v>MOD-01-TS-001_TC003_Validate text input submission at edge level</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="J4" s="7">
+        <v>2</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="I4" s="7">
-        <v>2</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="O4" s="7" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="R4" s="7"/>
+        <v>312</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="S4" s="7"/>
-    </row>
-    <row r="5" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+      <c r="T4" s="7"/>
+    </row>
+    <row r="5" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>110</v>
       </c>
@@ -4268,40 +4264,45 @@
         <v>139</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-002_Tc001_ValidateCheckboxSelectionAndDeselection</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A5,E5,F5)</f>
+        <v>MOD-01-TS-002_TC001_Validate checkbox selection and deselection</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="7">
-        <v>2</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
-    </row>
-    <row r="6" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>110</v>
       </c>
@@ -4315,40 +4316,45 @@
         <v>139</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="H6" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-002_Ts001_VerifyBehaviorOfPartiallySelectedCheckboxes</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A6,E6,F6)</f>
+        <v>MOD-01-TS-002_TS001_Verify behavior of partially selected checkboxes</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="L6" s="7" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="N6" s="7"/>
+        <v>261</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
-    </row>
-    <row r="7" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="T6" s="7"/>
+    </row>
+    <row r="7" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>111</v>
       </c>
@@ -4362,40 +4368,45 @@
         <v>140</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H7" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-003_Ts001_ValidateRadioButtonSelectionBehavior</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A7,E7,F7)</f>
+        <v>MOD-01-TS-003_TS001_Validate radio button selection behavior</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>321</v>
-      </c>
       <c r="L7" s="7" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="N7" s="7"/>
+        <v>264</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>265</v>
+      </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
-    </row>
-    <row r="8" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="T7" s="7"/>
+    </row>
+    <row r="8" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>112</v>
       </c>
@@ -4409,40 +4420,45 @@
         <v>141</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="H8" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-004_Ts001_ValidateAddingANewRecord</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A8,E8,F8)</f>
+        <v>MOD-01-TS-004_TS001_Validate adding a new record</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="7">
         <v>4</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="L8" s="7" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="N8" s="7"/>
+        <v>267</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>268</v>
+      </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
-    </row>
-    <row r="9" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T8" s="7"/>
+    </row>
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>112</v>
       </c>
@@ -4456,40 +4472,45 @@
         <v>141</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="H9" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-004_Ts002_ValidateSearchFunctionality</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A9,E9,F9)</f>
+        <v>MOD-01-TS-004_TS002_Validate search functionality</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="7">
+      <c r="J9" s="7">
         <v>4</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="L9" s="7" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="N9" s="7"/>
+        <v>270</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>271</v>
+      </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
-    </row>
-    <row r="10" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T9" s="7"/>
+    </row>
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>112</v>
       </c>
@@ -4503,40 +4524,45 @@
         <v>141</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="H10" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-004_Ts003_VerifyEditFunctionality</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A10,E10,F10)</f>
+        <v>MOD-01-TS-004_TS003_Verify edit functionality</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <v>4</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="L10" s="7" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="N10" s="7"/>
+        <v>273</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
-    </row>
-    <row r="11" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T10" s="7"/>
+    </row>
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>112</v>
       </c>
@@ -4550,40 +4576,45 @@
         <v>141</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>283</v>
+        <v>330</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="H11" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-004_Ts004_VerifyRecordDeletion</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A11,E11,F11)</f>
+        <v>MOD-01-TS-004_TS004_Verify record deletion</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="7">
+      <c r="J11" s="7">
         <v>4</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="L11" s="7" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="N11" s="7"/>
+        <v>276</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>277</v>
+      </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
-    </row>
-    <row r="12" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T11" s="7"/>
+    </row>
+    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>113</v>
       </c>
@@ -4597,42 +4628,47 @@
         <v>142</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="H12" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="G12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-005_Tc001_ValidateNormalButtonClick</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A12,E12,F12)</f>
+        <v>MOD-01-TS-005_TC001_Validate normal button click</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="7">
+      <c r="J12" s="7">
         <v>3</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="L12" s="7" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="N12" s="7"/>
+        <v>279</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>280</v>
+      </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
-    </row>
-    <row r="13" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T12" s="7"/>
+    </row>
+    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>52</v>
@@ -4644,42 +4680,47 @@
         <v>142</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="H13" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-005_Tc002_ValidateDouble-ClickFunctionality</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A13,E13,F13)</f>
+        <v>MOD-01-TS-005_TC002_Validate double-click functionality</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="7">
+      <c r="J13" s="7">
         <v>3</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="L13" s="7" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="N13" s="7"/>
+        <v>282</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
-    </row>
-    <row r="14" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T13" s="7"/>
+    </row>
+    <row r="14" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>52</v>
@@ -4691,40 +4732,45 @@
         <v>142</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="H14" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G14" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-005_Tc003_ValidateRight-ClickFunctionality</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A14,E14,F14)</f>
+        <v>MOD-01-TS-005_TC003_Validate right-click functionality</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="7">
+      <c r="J14" s="7">
         <v>3</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="K14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>323</v>
-      </c>
       <c r="L14" s="7" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="N14" s="7"/>
+        <v>285</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>286</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
-    </row>
-    <row r="15" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>114</v>
       </c>
@@ -4738,40 +4784,45 @@
         <v>143</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="H15" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-006_Tc001_ValidateWorkingLinks</v>
+      </c>
+      <c r="H15" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A15,E15,F15)</f>
+        <v>MOD-01-TS-006_TC001_Validate working links</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="7">
         <v>2</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="K15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>324</v>
-      </c>
       <c r="L15" s="7" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="N15" s="7"/>
+        <v>288</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
-    </row>
-    <row r="16" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>114</v>
       </c>
@@ -4785,40 +4836,45 @@
         <v>143</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I16" s="7">
+        <v>290</v>
+      </c>
+      <c r="G16" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-006_Tc002_ValidateBrokenLinkBehavior</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A16,E16,F16)</f>
+        <v>MOD-01-TS-006_TC002_Validate broken link behavior</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="J16" s="7">
         <v>2</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="K16" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>324</v>
-      </c>
       <c r="L16" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="N16" s="7"/>
+        <v>291</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>292</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
-    </row>
-    <row r="17" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>115</v>
       </c>
@@ -4832,40 +4888,45 @@
         <v>144</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-007_Tc001_ValidateFileUpload</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A17,E17,F17)</f>
+        <v>MOD-01-TS-007_TC001_Validate file upload</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="7">
+        <v>2</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="7">
-        <v>2</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>309</v>
-      </c>
       <c r="M17" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="N17" s="7"/>
+        <v>294</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>295</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
-    </row>
-    <row r="18" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T17" s="7"/>
+    </row>
+    <row r="18" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>115</v>
       </c>
@@ -4879,40 +4940,45 @@
         <v>144</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="H18" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G18" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-007_Tc002_ValidateFileDownload</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A18,E18,F18)</f>
+        <v>MOD-01-TS-007_TC002_Validate file download</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="7">
+      <c r="J18" s="7">
         <v>2</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="K18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>325</v>
-      </c>
       <c r="L18" s="7" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="N18" s="7"/>
+        <v>297</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>298</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
-    </row>
-    <row r="19" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T18" s="7"/>
+    </row>
+    <row r="19" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>116</v>
       </c>
@@ -4926,40 +4992,45 @@
         <v>145</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="H19" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G19" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-01-Ts-008_Tc001_ValidateDynamicButtonAppearance</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A19,E19,F19)</f>
+        <v>MOD-01-TS-008_TC001_Validate dynamic button appearance</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="7">
+      <c r="J19" s="7">
         <v>1</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>326</v>
-      </c>
       <c r="L19" s="7" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="N19" s="7"/>
+        <v>300</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
-    </row>
-    <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>117</v>
       </c>
@@ -4972,10 +5043,20 @@
       <c r="D20" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G20" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-02-Ts-001_Tc001_ValidateFormsInputsAndSubmissions</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A20,E20,F20)</f>
+        <v>MOD-02-TS-001_TC001_Validate forms inputs and submissions</v>
+      </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -4987,8 +5068,9 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>118</v>
       </c>
@@ -5001,10 +5083,18 @@
       <c r="D21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="G21" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-03-Ts-001_Tc001</v>
+      </c>
+      <c r="H21" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A21,E21,F21)</f>
+        <v>MOD-03-TS-001_TC001</v>
+      </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -5016,8 +5106,9 @@
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
-    </row>
-    <row r="22" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>119</v>
       </c>
@@ -5030,10 +5121,18 @@
       <c r="D22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="G22" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-03-Ts-002_Tc001</v>
+      </c>
+      <c r="H22" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A22,E22,F22)</f>
+        <v>MOD-03-TS-002_TC001</v>
+      </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -5045,8 +5144,9 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
-    </row>
-    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>120</v>
       </c>
@@ -5059,10 +5159,18 @@
       <c r="D23" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="G23" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-03-Ts-003_Tc001</v>
+      </c>
+      <c r="H23" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A23,E23,F23)</f>
+        <v>MOD-03-TS-003_TC001</v>
+      </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -5074,8 +5182,9 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
-    </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>121</v>
       </c>
@@ -5088,10 +5197,18 @@
       <c r="D24" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="G24" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-04-Ts-001_Tc001</v>
+      </c>
+      <c r="H24" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A24,E24,F24)</f>
+        <v>MOD-04-TS-001_TC001</v>
+      </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -5103,8 +5220,9 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
-    </row>
-    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>122</v>
       </c>
@@ -5117,10 +5235,18 @@
       <c r="D25" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-04-Ts-002_Tc001</v>
+      </c>
+      <c r="H25" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A25,E25,F25)</f>
+        <v>MOD-04-TS-002_TC001</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -5132,8 +5258,9 @@
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
-    </row>
-    <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>123</v>
       </c>
@@ -5146,10 +5273,18 @@
       <c r="D26" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="G26" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-04-Ts-003_Tc001</v>
+      </c>
+      <c r="H26" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A26,E26,F26)</f>
+        <v>MOD-04-TS-003_TC001</v>
+      </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -5161,8 +5296,9 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
-    </row>
-    <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T26" s="7"/>
+    </row>
+    <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>124</v>
       </c>
@@ -5175,10 +5311,18 @@
       <c r="D27" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-04-Ts-004_Tc001</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A27,E27,F27)</f>
+        <v>MOD-04-TS-004_TC001</v>
+      </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -5190,8 +5334,9 @@
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
-    </row>
-    <row r="28" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T27" s="7"/>
+    </row>
+    <row r="28" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>125</v>
       </c>
@@ -5204,10 +5349,18 @@
       <c r="D28" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="G28" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-04-Ts-005_Tc001</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A28,E28,F28)</f>
+        <v>MOD-04-TS-005_TC001</v>
+      </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
@@ -5219,8 +5372,9 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
-    </row>
-    <row r="29" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T28" s="7"/>
+    </row>
+    <row r="29" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>126</v>
       </c>
@@ -5233,10 +5387,18 @@
       <c r="D29" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="G29" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-05-Ts-001_Tc001</v>
+      </c>
+      <c r="H29" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A29,E29,F29)</f>
+        <v>MOD-05-TS-001_TC001</v>
+      </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -5248,8 +5410,9 @@
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
-    </row>
-    <row r="30" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T29" s="7"/>
+    </row>
+    <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>127</v>
       </c>
@@ -5262,10 +5425,18 @@
       <c r="D30" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="G30" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-05-Ts-002_Tc001</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A30,E30,F30)</f>
+        <v>MOD-05-TS-002_TC001</v>
+      </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -5277,8 +5448,9 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
-    </row>
-    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T30" s="7"/>
+    </row>
+    <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>128</v>
       </c>
@@ -5291,10 +5463,18 @@
       <c r="D31" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="G31" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-05-Ts-003_Tc001</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A31,E31,F31)</f>
+        <v>MOD-05-TS-003_TC001</v>
+      </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
@@ -5306,8 +5486,9 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
-    </row>
-    <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T31" s="7"/>
+    </row>
+    <row r="32" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>129</v>
       </c>
@@ -5320,10 +5501,18 @@
       <c r="D32" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="G32" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-06-Ts-001_Tc001</v>
+      </c>
+      <c r="H32" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A32,E32,F32)</f>
+        <v>MOD-06-TS-001_TC001</v>
+      </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
@@ -5335,8 +5524,9 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
-    </row>
-    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T32" s="7"/>
+    </row>
+    <row r="33" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>130</v>
       </c>
@@ -5349,10 +5539,18 @@
       <c r="D33" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="G33" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-06-Ts-002_Tc001</v>
+      </c>
+      <c r="H33" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A33,E33,F33)</f>
+        <v>MOD-06-TS-002_TC001</v>
+      </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -5364,8 +5562,9 @@
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
-    </row>
-    <row r="34" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T33" s="7"/>
+    </row>
+    <row r="34" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>131</v>
       </c>
@@ -5378,10 +5577,18 @@
       <c r="D34" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="G34" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-06-Ts-003_Tc001</v>
+      </c>
+      <c r="H34" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A34,E34,F34)</f>
+        <v>MOD-06-TS-003_TC001</v>
+      </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -5393,8 +5600,9 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
-    </row>
-    <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T34" s="7"/>
+    </row>
+    <row r="35" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>132</v>
       </c>
@@ -5407,10 +5615,18 @@
       <c r="D35" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="G35" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-001_Tc001</v>
+      </c>
+      <c r="H35" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A35,E35,F35)</f>
+        <v>MOD-07-TS-001_TC001</v>
+      </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
@@ -5422,8 +5638,9 @@
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
-    </row>
-    <row r="36" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T35" s="7"/>
+    </row>
+    <row r="36" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>133</v>
       </c>
@@ -5436,10 +5653,18 @@
       <c r="D36" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="G36" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-002_Tc001</v>
+      </c>
+      <c r="H36" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A36,E36,F36)</f>
+        <v>MOD-07-TS-002_TC001</v>
+      </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
@@ -5451,8 +5676,9 @@
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
       <c r="S36" s="7"/>
-    </row>
-    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T36" s="7"/>
+    </row>
+    <row r="37" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>134</v>
       </c>
@@ -5465,10 +5691,18 @@
       <c r="D37" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E37" s="7"/>
+      <c r="E37" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="G37" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-003_Tc001</v>
+      </c>
+      <c r="H37" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A37,E37,F37)</f>
+        <v>MOD-07-TS-003_TC001</v>
+      </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
@@ -5480,8 +5714,9 @@
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
-    </row>
-    <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T37" s="7"/>
+    </row>
+    <row r="38" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>135</v>
       </c>
@@ -5494,10 +5729,18 @@
       <c r="D38" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+      <c r="G38" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-004_Tc001</v>
+      </c>
+      <c r="H38" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A38,E38,F38)</f>
+        <v>MOD-07-TS-004_TC001</v>
+      </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -5509,8 +5752,9 @@
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-    </row>
-    <row r="39" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T38" s="7"/>
+    </row>
+    <row r="39" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>136</v>
       </c>
@@ -5523,10 +5767,18 @@
       <c r="D39" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E39" s="7"/>
+      <c r="E39" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="G39" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-005_Tc001</v>
+      </c>
+      <c r="H39" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A39,E39,F39)</f>
+        <v>MOD-07-TS-005_TC001</v>
+      </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
@@ -5538,8 +5790,9 @@
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-    </row>
-    <row r="40" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T39" s="7"/>
+    </row>
+    <row r="40" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>137</v>
       </c>
@@ -5552,10 +5805,18 @@
       <c r="D40" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E40" s="7"/>
+      <c r="E40" s="7" t="s">
+        <v>324</v>
+      </c>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
+      <c r="G40" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>Mod-07-Ts-006_Tc001</v>
+      </c>
+      <c r="H40" s="7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,A40,E40,F40)</f>
+        <v>MOD-07-TS-006_TC001</v>
+      </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -5567,33 +5828,7 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K43" s="7"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K46" s="7"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K49" s="7"/>
+      <c r="T40" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
